--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,1655 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129390498</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>527427</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6942627</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129390485</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>527414</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6942677</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129390497</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>527319</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6942639</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129390504</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>527467</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6942755</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129390489</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>527422</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6942496</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129390494</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>527307</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6942738</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129390512</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92821</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>527361</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6942734</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129390495</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>527279</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6942673</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129390500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>527421</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6942686</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129390511</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92821</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>527389</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6942744</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129390510</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78707</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>353</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>527467</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6942755</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129390513</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92821</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>527306</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6942482</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129390491</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78799</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>527467</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6942757</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129390503</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>527464</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6942743</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129390505</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>527493</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6942824</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129390490</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78799</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>527420</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6942696</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129390499</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dysjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>527432</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6942682</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>129390512</v>
       </c>
       <c r="B9" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129390511</v>
       </c>
       <c r="B12" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129390513</v>
       </c>
       <c r="B14" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390503</v>
+        <v>129390490</v>
       </c>
       <c r="B16" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527464</v>
+        <v>527420</v>
       </c>
       <c r="R16" t="n">
-        <v>6942743</v>
+        <v>6942696</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390505</v>
+        <v>129390503</v>
       </c>
       <c r="B17" t="n">
         <v>78798</v>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527493</v>
+        <v>527464</v>
       </c>
       <c r="R17" t="n">
-        <v>6942824</v>
+        <v>6942743</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390490</v>
+        <v>129390505</v>
       </c>
       <c r="B18" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527420</v>
+        <v>527493</v>
       </c>
       <c r="R18" t="n">
-        <v>6942696</v>
+        <v>6942824</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129390498</v>
       </c>
       <c r="B3" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129390485</v>
       </c>
       <c r="B4" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129390497</v>
       </c>
       <c r="B5" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129390504</v>
       </c>
       <c r="B6" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>129390494</v>
       </c>
       <c r="B8" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>129390512</v>
       </c>
       <c r="B9" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>129390495</v>
       </c>
       <c r="B10" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129390500</v>
       </c>
       <c r="B11" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129390511</v>
       </c>
       <c r="B12" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129390510</v>
       </c>
       <c r="B13" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129390513</v>
       </c>
       <c r="B14" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129390491</v>
       </c>
       <c r="B15" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390490</v>
+        <v>129390503</v>
       </c>
       <c r="B16" t="n">
-        <v>78799</v>
+        <v>78800</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527420</v>
+        <v>527464</v>
       </c>
       <c r="R16" t="n">
-        <v>6942696</v>
+        <v>6942743</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390503</v>
+        <v>129390505</v>
       </c>
       <c r="B17" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527464</v>
+        <v>527493</v>
       </c>
       <c r="R17" t="n">
-        <v>6942743</v>
+        <v>6942824</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390505</v>
+        <v>129390490</v>
       </c>
       <c r="B18" t="n">
-        <v>78798</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527493</v>
+        <v>527420</v>
       </c>
       <c r="R18" t="n">
-        <v>6942824</v>
+        <v>6942696</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2359,7 +2359,7 @@
         <v>129390499</v>
       </c>
       <c r="B19" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129390498</v>
       </c>
       <c r="B3" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129390485</v>
       </c>
       <c r="B4" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129390497</v>
       </c>
       <c r="B5" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129390504</v>
       </c>
       <c r="B6" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>129390494</v>
       </c>
       <c r="B8" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>129390512</v>
       </c>
       <c r="B9" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>129390495</v>
       </c>
       <c r="B10" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129390500</v>
       </c>
       <c r="B11" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129390511</v>
       </c>
       <c r="B12" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129390510</v>
       </c>
       <c r="B13" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129390513</v>
       </c>
       <c r="B14" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129390491</v>
       </c>
       <c r="B15" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>129390503</v>
       </c>
       <c r="B16" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>129390505</v>
       </c>
       <c r="B17" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129390490</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>129390499</v>
       </c>
       <c r="B19" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>129390512</v>
       </c>
       <c r="B9" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129390511</v>
       </c>
       <c r="B12" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129390513</v>
       </c>
       <c r="B14" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390503</v>
+        <v>129390490</v>
       </c>
       <c r="B16" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527464</v>
+        <v>527420</v>
       </c>
       <c r="R16" t="n">
-        <v>6942743</v>
+        <v>6942696</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390505</v>
+        <v>129390503</v>
       </c>
       <c r="B17" t="n">
         <v>78801</v>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527493</v>
+        <v>527464</v>
       </c>
       <c r="R17" t="n">
-        <v>6942824</v>
+        <v>6942743</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390490</v>
+        <v>129390505</v>
       </c>
       <c r="B18" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527420</v>
+        <v>527493</v>
       </c>
       <c r="R18" t="n">
-        <v>6942696</v>
+        <v>6942824</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129390497</v>
+        <v>129390504</v>
       </c>
       <c r="B5" t="n">
         <v>78801</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527319</v>
+        <v>527467</v>
       </c>
       <c r="R5" t="n">
-        <v>6942639</v>
+        <v>6942755</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129390504</v>
+        <v>129390497</v>
       </c>
       <c r="B6" t="n">
         <v>78801</v>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527467</v>
+        <v>527319</v>
       </c>
       <c r="R6" t="n">
-        <v>6942755</v>
+        <v>6942639</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1389,7 +1389,7 @@
         <v>129390512</v>
       </c>
       <c r="B9" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129390511</v>
       </c>
       <c r="B12" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129390513</v>
       </c>
       <c r="B14" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390490</v>
+        <v>129390505</v>
       </c>
       <c r="B16" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527420</v>
+        <v>527493</v>
       </c>
       <c r="R16" t="n">
-        <v>6942696</v>
+        <v>6942824</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390505</v>
+        <v>129390490</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527493</v>
+        <v>527420</v>
       </c>
       <c r="R18" t="n">
-        <v>6942824</v>
+        <v>6942696</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129390504</v>
+        <v>129390497</v>
       </c>
       <c r="B5" t="n">
         <v>78801</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527467</v>
+        <v>527319</v>
       </c>
       <c r="R5" t="n">
-        <v>6942755</v>
+        <v>6942639</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129390497</v>
+        <v>129390504</v>
       </c>
       <c r="B6" t="n">
         <v>78801</v>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527319</v>
+        <v>527467</v>
       </c>
       <c r="R6" t="n">
-        <v>6942639</v>
+        <v>6942755</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390505</v>
+        <v>129390503</v>
       </c>
       <c r="B16" t="n">
         <v>78801</v>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527493</v>
+        <v>527464</v>
       </c>
       <c r="R16" t="n">
-        <v>6942824</v>
+        <v>6942743</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390503</v>
+        <v>129390505</v>
       </c>
       <c r="B17" t="n">
         <v>78801</v>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527464</v>
+        <v>527493</v>
       </c>
       <c r="R17" t="n">
-        <v>6942743</v>
+        <v>6942824</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129390497</v>
+        <v>129390504</v>
       </c>
       <c r="B5" t="n">
         <v>78801</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527319</v>
+        <v>527467</v>
       </c>
       <c r="R5" t="n">
-        <v>6942639</v>
+        <v>6942755</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129390504</v>
+        <v>129390497</v>
       </c>
       <c r="B6" t="n">
         <v>78801</v>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527467</v>
+        <v>527319</v>
       </c>
       <c r="R6" t="n">
-        <v>6942755</v>
+        <v>6942639</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1389,7 +1389,7 @@
         <v>129390512</v>
       </c>
       <c r="B9" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129390511</v>
       </c>
       <c r="B12" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129390513</v>
       </c>
       <c r="B14" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390503</v>
+        <v>129390505</v>
       </c>
       <c r="B16" t="n">
         <v>78801</v>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527464</v>
+        <v>527493</v>
       </c>
       <c r="R16" t="n">
-        <v>6942743</v>
+        <v>6942824</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390505</v>
+        <v>129390503</v>
       </c>
       <c r="B17" t="n">
         <v>78801</v>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527493</v>
+        <v>527464</v>
       </c>
       <c r="R17" t="n">
-        <v>6942824</v>
+        <v>6942743</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129390504</v>
+        <v>129390497</v>
       </c>
       <c r="B5" t="n">
         <v>78801</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527467</v>
+        <v>527319</v>
       </c>
       <c r="R5" t="n">
-        <v>6942755</v>
+        <v>6942639</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129390497</v>
+        <v>129390504</v>
       </c>
       <c r="B6" t="n">
         <v>78801</v>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527319</v>
+        <v>527467</v>
       </c>
       <c r="R6" t="n">
-        <v>6942639</v>
+        <v>6942755</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129390513</v>
+        <v>129390491</v>
       </c>
       <c r="B14" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527306</v>
+        <v>527467</v>
       </c>
       <c r="R14" t="n">
-        <v>6942482</v>
+        <v>6942757</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129390491</v>
+        <v>129390513</v>
       </c>
       <c r="B15" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527467</v>
+        <v>527306</v>
       </c>
       <c r="R15" t="n">
-        <v>6942757</v>
+        <v>6942482</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390505</v>
+        <v>129390490</v>
       </c>
       <c r="B16" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527493</v>
+        <v>527420</v>
       </c>
       <c r="R16" t="n">
-        <v>6942824</v>
+        <v>6942696</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390490</v>
+        <v>129390505</v>
       </c>
       <c r="B18" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527420</v>
+        <v>527493</v>
       </c>
       <c r="R18" t="n">
-        <v>6942696</v>
+        <v>6942824</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129390491</v>
+        <v>129390513</v>
       </c>
       <c r="B14" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527467</v>
+        <v>527306</v>
       </c>
       <c r="R14" t="n">
-        <v>6942757</v>
+        <v>6942482</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129390513</v>
+        <v>129390491</v>
       </c>
       <c r="B15" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527306</v>
+        <v>527467</v>
       </c>
       <c r="R15" t="n">
-        <v>6942482</v>
+        <v>6942757</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129390513</v>
+        <v>129390491</v>
       </c>
       <c r="B14" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527306</v>
+        <v>527467</v>
       </c>
       <c r="R14" t="n">
-        <v>6942482</v>
+        <v>6942757</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129390491</v>
+        <v>129390513</v>
       </c>
       <c r="B15" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527467</v>
+        <v>527306</v>
       </c>
       <c r="R15" t="n">
-        <v>6942757</v>
+        <v>6942482</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129390491</v>
+        <v>129390513</v>
       </c>
       <c r="B14" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527467</v>
+        <v>527306</v>
       </c>
       <c r="R14" t="n">
-        <v>6942757</v>
+        <v>6942482</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129390513</v>
+        <v>129390491</v>
       </c>
       <c r="B15" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527306</v>
+        <v>527467</v>
       </c>
       <c r="R15" t="n">
-        <v>6942482</v>
+        <v>6942757</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390490</v>
+        <v>129390503</v>
       </c>
       <c r="B16" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527420</v>
+        <v>527464</v>
       </c>
       <c r="R16" t="n">
-        <v>6942696</v>
+        <v>6942743</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390503</v>
+        <v>129390505</v>
       </c>
       <c r="B17" t="n">
         <v>78801</v>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527464</v>
+        <v>527493</v>
       </c>
       <c r="R17" t="n">
-        <v>6942743</v>
+        <v>6942824</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390505</v>
+        <v>129390490</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527493</v>
+        <v>527420</v>
       </c>
       <c r="R18" t="n">
-        <v>6942824</v>
+        <v>6942696</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129390498</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129390485</v>
       </c>
       <c r="B4" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129390497</v>
+        <v>129390504</v>
       </c>
       <c r="B5" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527319</v>
+        <v>527467</v>
       </c>
       <c r="R5" t="n">
-        <v>6942639</v>
+        <v>6942755</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129390504</v>
+        <v>129390497</v>
       </c>
       <c r="B6" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527467</v>
+        <v>527319</v>
       </c>
       <c r="R6" t="n">
-        <v>6942755</v>
+        <v>6942639</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1195,7 +1195,7 @@
         <v>129390489</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>129390494</v>
       </c>
       <c r="B8" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>129390512</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>129390495</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129390500</v>
       </c>
       <c r="B11" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129390511</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129390510</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129390491</v>
       </c>
       <c r="B14" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129390513</v>
       </c>
       <c r="B15" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390503</v>
+        <v>129390505</v>
       </c>
       <c r="B16" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527464</v>
+        <v>527493</v>
       </c>
       <c r="R16" t="n">
-        <v>6942743</v>
+        <v>6942824</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390505</v>
+        <v>129390503</v>
       </c>
       <c r="B17" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527493</v>
+        <v>527464</v>
       </c>
       <c r="R17" t="n">
-        <v>6942824</v>
+        <v>6942743</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2262,7 +2262,7 @@
         <v>129390490</v>
       </c>
       <c r="B18" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>129390499</v>
       </c>
       <c r="B19" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390505</v>
+        <v>129390490</v>
       </c>
       <c r="B16" t="n">
-        <v>78827</v>
+        <v>78828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527493</v>
+        <v>527420</v>
       </c>
       <c r="R16" t="n">
-        <v>6942824</v>
+        <v>6942696</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390503</v>
+        <v>129390505</v>
       </c>
       <c r="B17" t="n">
         <v>78827</v>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527464</v>
+        <v>527493</v>
       </c>
       <c r="R17" t="n">
-        <v>6942743</v>
+        <v>6942824</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390490</v>
+        <v>129390503</v>
       </c>
       <c r="B18" t="n">
-        <v>78828</v>
+        <v>78827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527420</v>
+        <v>527464</v>
       </c>
       <c r="R18" t="n">
-        <v>6942696</v>
+        <v>6942743</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129390498</v>
       </c>
       <c r="B3" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129390485</v>
       </c>
       <c r="B4" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129390504</v>
+        <v>129390497</v>
       </c>
       <c r="B5" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527467</v>
+        <v>527319</v>
       </c>
       <c r="R5" t="n">
-        <v>6942755</v>
+        <v>6942639</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129390497</v>
+        <v>129390504</v>
       </c>
       <c r="B6" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527319</v>
+        <v>527467</v>
       </c>
       <c r="R6" t="n">
-        <v>6942639</v>
+        <v>6942755</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1195,7 +1195,7 @@
         <v>129390489</v>
       </c>
       <c r="B7" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>129390494</v>
       </c>
       <c r="B8" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>129390512</v>
       </c>
       <c r="B9" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>129390495</v>
       </c>
       <c r="B10" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129390500</v>
       </c>
       <c r="B11" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129390511</v>
       </c>
       <c r="B12" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129390510</v>
       </c>
       <c r="B13" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129390491</v>
+        <v>129390513</v>
       </c>
       <c r="B14" t="n">
-        <v>78828</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527467</v>
+        <v>527306</v>
       </c>
       <c r="R14" t="n">
-        <v>6942757</v>
+        <v>6942482</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129390513</v>
+        <v>129390491</v>
       </c>
       <c r="B15" t="n">
-        <v>92863</v>
+        <v>78833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527306</v>
+        <v>527467</v>
       </c>
       <c r="R15" t="n">
-        <v>6942482</v>
+        <v>6942757</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390490</v>
+        <v>129390503</v>
       </c>
       <c r="B16" t="n">
-        <v>78828</v>
+        <v>78832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527420</v>
+        <v>527464</v>
       </c>
       <c r="R16" t="n">
-        <v>6942696</v>
+        <v>6942743</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2165,7 +2165,7 @@
         <v>129390505</v>
       </c>
       <c r="B17" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390503</v>
+        <v>129390490</v>
       </c>
       <c r="B18" t="n">
-        <v>78827</v>
+        <v>78833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527464</v>
+        <v>527420</v>
       </c>
       <c r="R18" t="n">
-        <v>6942743</v>
+        <v>6942696</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2359,7 +2359,7 @@
         <v>129390499</v>
       </c>
       <c r="B19" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129390498</v>
       </c>
       <c r="B3" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129390485</v>
       </c>
       <c r="B4" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129390497</v>
       </c>
       <c r="B5" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129390504</v>
       </c>
       <c r="B6" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129390489</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>129390494</v>
       </c>
       <c r="B8" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>129390512</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>129390495</v>
       </c>
       <c r="B10" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129390500</v>
       </c>
       <c r="B11" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129390511</v>
       </c>
       <c r="B12" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129390510</v>
       </c>
       <c r="B13" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129390513</v>
       </c>
       <c r="B14" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129390491</v>
       </c>
       <c r="B15" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390503</v>
+        <v>129390490</v>
       </c>
       <c r="B16" t="n">
-        <v>78832</v>
+        <v>78834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527464</v>
+        <v>527420</v>
       </c>
       <c r="R16" t="n">
-        <v>6942743</v>
+        <v>6942696</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390505</v>
+        <v>129390503</v>
       </c>
       <c r="B17" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527493</v>
+        <v>527464</v>
       </c>
       <c r="R17" t="n">
-        <v>6942824</v>
+        <v>6942743</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390490</v>
+        <v>129390505</v>
       </c>
       <c r="B18" t="n">
         <v>78833</v>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527420</v>
+        <v>527493</v>
       </c>
       <c r="R18" t="n">
-        <v>6942696</v>
+        <v>6942824</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2359,7 +2359,7 @@
         <v>129390499</v>
       </c>
       <c r="B19" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390490</v>
+        <v>129390503</v>
       </c>
       <c r="B16" t="n">
-        <v>78834</v>
+        <v>78833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527420</v>
+        <v>527464</v>
       </c>
       <c r="R16" t="n">
-        <v>6942696</v>
+        <v>6942743</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390503</v>
+        <v>129390505</v>
       </c>
       <c r="B17" t="n">
         <v>78833</v>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527464</v>
+        <v>527493</v>
       </c>
       <c r="R17" t="n">
-        <v>6942743</v>
+        <v>6942824</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390505</v>
+        <v>129390490</v>
       </c>
       <c r="B18" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527493</v>
+        <v>527420</v>
       </c>
       <c r="R18" t="n">
-        <v>6942824</v>
+        <v>6942696</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129390498</v>
       </c>
       <c r="B3" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129390485</v>
       </c>
       <c r="B4" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129390497</v>
       </c>
       <c r="B5" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129390504</v>
       </c>
       <c r="B6" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>129390494</v>
       </c>
       <c r="B8" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>129390512</v>
       </c>
       <c r="B9" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>129390495</v>
       </c>
       <c r="B10" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129390500</v>
       </c>
       <c r="B11" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129390511</v>
       </c>
       <c r="B12" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129390510</v>
       </c>
       <c r="B13" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129390513</v>
       </c>
       <c r="B14" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>129390491</v>
       </c>
       <c r="B15" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390503</v>
+        <v>129390490</v>
       </c>
       <c r="B16" t="n">
-        <v>78833</v>
+        <v>78839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527464</v>
+        <v>527420</v>
       </c>
       <c r="R16" t="n">
-        <v>6942743</v>
+        <v>6942696</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390505</v>
+        <v>129390503</v>
       </c>
       <c r="B17" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527493</v>
+        <v>527464</v>
       </c>
       <c r="R17" t="n">
-        <v>6942824</v>
+        <v>6942743</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390490</v>
+        <v>129390505</v>
       </c>
       <c r="B18" t="n">
-        <v>78834</v>
+        <v>78838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527420</v>
+        <v>527493</v>
       </c>
       <c r="R18" t="n">
-        <v>6942696</v>
+        <v>6942824</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2359,7 +2359,7 @@
         <v>129390499</v>
       </c>
       <c r="B19" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390490</v>
+        <v>129390503</v>
       </c>
       <c r="B16" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527420</v>
+        <v>527464</v>
       </c>
       <c r="R16" t="n">
-        <v>6942696</v>
+        <v>6942743</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390503</v>
+        <v>129390505</v>
       </c>
       <c r="B17" t="n">
         <v>78838</v>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527464</v>
+        <v>527493</v>
       </c>
       <c r="R17" t="n">
-        <v>6942743</v>
+        <v>6942824</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390505</v>
+        <v>129390490</v>
       </c>
       <c r="B18" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527493</v>
+        <v>527420</v>
       </c>
       <c r="R18" t="n">
-        <v>6942824</v>
+        <v>6942696</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129390497</v>
+        <v>129390504</v>
       </c>
       <c r="B5" t="n">
         <v>78838</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527319</v>
+        <v>527467</v>
       </c>
       <c r="R5" t="n">
-        <v>6942639</v>
+        <v>6942755</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129390504</v>
+        <v>129390497</v>
       </c>
       <c r="B6" t="n">
         <v>78838</v>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527467</v>
+        <v>527319</v>
       </c>
       <c r="R6" t="n">
-        <v>6942755</v>
+        <v>6942639</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1389,7 +1389,7 @@
         <v>129390512</v>
       </c>
       <c r="B9" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129390511</v>
       </c>
       <c r="B12" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129390513</v>
+        <v>129390491</v>
       </c>
       <c r="B14" t="n">
-        <v>92875</v>
+        <v>78839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527306</v>
+        <v>527467</v>
       </c>
       <c r="R14" t="n">
-        <v>6942482</v>
+        <v>6942757</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129390491</v>
+        <v>129390513</v>
       </c>
       <c r="B15" t="n">
-        <v>78839</v>
+        <v>92879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527467</v>
+        <v>527306</v>
       </c>
       <c r="R15" t="n">
-        <v>6942757</v>
+        <v>6942482</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129390503</v>
+        <v>129390505</v>
       </c>
       <c r="B16" t="n">
         <v>78838</v>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527464</v>
+        <v>527493</v>
       </c>
       <c r="R16" t="n">
-        <v>6942743</v>
+        <v>6942824</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129390505</v>
+        <v>129390490</v>
       </c>
       <c r="B17" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,21 +2173,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527493</v>
+        <v>527420</v>
       </c>
       <c r="R17" t="n">
-        <v>6942824</v>
+        <v>6942696</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129390490</v>
+        <v>129390503</v>
       </c>
       <c r="B18" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527420</v>
+        <v>527464</v>
       </c>
       <c r="R18" t="n">
-        <v>6942696</v>
+        <v>6942743</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 48191-2025 artfynd.xlsx
+++ b/artfynd/A 48191-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441780</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441781</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390510</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390511</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390512</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390513</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390508</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390509</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390494</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1681,6 +1731,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390495</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1778,6 +1833,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390497</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1875,6 +1935,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390498</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1972,6 +2037,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390499</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2069,6 +2139,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390500</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2166,6 +2241,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390502</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2263,6 +2343,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390503</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2360,6 +2445,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390504</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2457,6 +2547,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390505</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2554,6 +2649,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390507</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2651,6 +2751,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390485</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2765,6 +2870,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441782</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2862,6 +2972,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390489</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2959,6 +3074,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390490</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3056,8 +3176,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129390491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>